--- a/debug/excel_overviews/gpt-4.1_vs_Mistral-7B-Instruct-v0.2/Qwen3-Next-80B-A3B-Instruct/default/total_votes_file.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_Mistral-7B-Instruct-v0.2/Qwen3-Next-80B-A3B-Instruct/default/total_votes_file.xlsx
@@ -430,16 +430,16 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>319</v>
+        <v>263</v>
       </c>
       <c r="D2">
-        <v>32</v>
+        <v>135</v>
       </c>
       <c r="E2">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="G2">
-        <v>57</v>
+        <v>25</v>
       </c>
       <c r="H2">
         <v>426</v>
@@ -450,16 +450,16 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>186</v>
+        <v>354</v>
       </c>
       <c r="D3">
-        <v>97</v>
+        <v>43</v>
       </c>
       <c r="E3">
-        <v>48</v>
+        <v>1</v>
       </c>
       <c r="G3">
-        <v>95</v>
+        <v>28</v>
       </c>
       <c r="H3">
         <v>426</v>

--- a/debug/excel_overviews/gpt-4.1_vs_Mistral-7B-Instruct-v0.2/Qwen3-Next-80B-A3B-Instruct/default/total_votes_file.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_Mistral-7B-Instruct-v0.2/Qwen3-Next-80B-A3B-Instruct/default/total_votes_file.xlsx
@@ -430,16 +430,16 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="D2">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="E2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G2">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="H2">
         <v>426</v>
@@ -450,13 +450,13 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>354</v>
+        <v>346</v>
       </c>
       <c r="D3">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G3">
         <v>28</v>
